--- a/data/trans_bre/IP18A05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 2,3</t>
+          <t>-1,72; 2,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,27; -0,07</t>
+          <t>-5,22; -0,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,36</t>
+          <t>-0,5; 4,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,51</t>
+          <t>0,0; 22,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,0</t>
+          <t>-1,91; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,46</t>
+          <t>-1,37; 1,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,5</t>
+          <t>-1,13; 2,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,5; -1,89</t>
+          <t>-14,36; -1,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-77,7; —</t>
+          <t>-75,51; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,0</t>
+          <t>-1,64; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,11</t>
+          <t>-0,43; 3,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 0,7</t>
+          <t>-6,11; 0,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 6,26</t>
+          <t>-17,61; 7,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,43</t>
+          <t>-1,17; 2,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,2</t>
+          <t>-1,59; 1,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 0,82</t>
+          <t>-2,26; 0,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,05</t>
+          <t>0,0; 9,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,85</t>
+          <t>-0,72; 0,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,55</t>
+          <t>-1,1; 0,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,87</t>
+          <t>-1,32; 0,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 2,44</t>
+          <t>-6,24; 2,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-76,8; 389,36</t>
+          <t>-81,27; 358,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-73,59; 98,6</t>
+          <t>-73,8; 82,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-65,93; 126,33</t>
+          <t>-67,66; 105,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-89,06; 125,86</t>
+          <t>-90,42; 142,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 2,41</t>
+          <t>-1,72; 2,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,22; -0,28</t>
+          <t>-5,12; -0,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 4,7</t>
+          <t>-0,49; 4,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,89</t>
+          <t>0,0; 22,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 150,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,0</t>
+          <t>-1,92; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,5</t>
+          <t>-1,45; 1,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,23</t>
+          <t>-1,11; 2,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,36; -1,75</t>
+          <t>-16,84; -1,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,51; —</t>
+          <t>-75,87; 999,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,0</t>
+          <t>-1,96; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,2</t>
+          <t>-0,44; 2,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 0,74</t>
+          <t>-5,91; 0,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 7,69</t>
+          <t>-18,28; 5,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 88,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,28</t>
+          <t>-1,06; 2,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,2</t>
+          <t>-1,57; 1,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 0,82</t>
+          <t>-2,34; 0,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,72</t>
+          <t>0,0; 9,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,85</t>
+          <t>-0,63; 0,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 0,54</t>
+          <t>-1,17; 0,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,81</t>
+          <t>-1,31; 0,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 2,35</t>
+          <t>-6,08; 2,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-81,27; 358,44</t>
+          <t>-80,02; 384,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-73,8; 82,69</t>
+          <t>-75,97; 103,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-67,66; 105,86</t>
+          <t>-68,33; 82,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-90,42; 142,83</t>
+          <t>-85,87; 135,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,76</t>
+          <t>6,1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 2,42</t>
+          <t>-1,69; 2,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,12; -0,09</t>
+          <t>-5,27; -0,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,6</t>
+          <t>-0,49; 4,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,95</t>
+          <t>0,0; 19,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 150,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,44</t>
+          <t>-6,8</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,0</t>
+          <t>-2,74; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,43</t>
+          <t>-1,43; 1,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 2,18</t>
+          <t>-1,06; 2,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,84; -1,78</t>
+          <t>-15,61; -2,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-75,87; 999,42</t>
+          <t>-77,7; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,35</t>
+          <t>-2,9</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-42,2%</t>
+          <t>-36,07%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 0,0</t>
+          <t>-1,9; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 2,77</t>
+          <t>-0,43; 3,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 0,61</t>
+          <t>-6,04; 0,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 5,61</t>
+          <t>-18,59; 7,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 88,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,5</t>
+          <t>-1,16; 2,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,55</t>
+          <t>-1,87; 1,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,74</t>
+          <t>-2,25; 0,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,81</t>
+          <t>0,0; 8,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-1,66</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-33,54%</t>
+          <t>-36,59%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,81</t>
+          <t>-0,66; 0,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,59</t>
+          <t>-1,15; 0,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,66</t>
+          <t>-1,32; 0,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 2,5</t>
+          <t>-7,05; 2,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-80,02; 384,51</t>
+          <t>-76,8; 389,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-75,97; 103,53</t>
+          <t>-73,59; 98,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-68,33; 82,77</t>
+          <t>-65,93; 126,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-85,87; 135,36</t>
+          <t>-90,42; 127,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP18A05-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,44 +619,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,41</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-2,3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>55,09%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-80,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>197,88%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>0.4105402180370586</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.300960432576812</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9538590412563303</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>6.103009208254822</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.5509390940267899</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.8014681933794351</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.978796177278561</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -655,254 +650,140 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-1,69; 2,3</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-5,27; -0,07</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-0,49; 4,36</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 19,28</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-1.693559105744597</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-5.265739139077717</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.4947432442976275</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.303576584896077</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>-0.0679752286051608</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>4.357049706575024</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>19.27825928130018</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,38</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,02</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-6,8</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>55,48%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,74; 0,0</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-1,43; 1,46</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,06; 2,5</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-15,61; -2,15</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-77,7; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.3807698569993169</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.01970979391529284</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.550685991490059</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-6.802497598245524</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.02762508821332599</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.5547875959257954</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,92</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,22</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,9</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>211,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-61,32%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-36,07%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.740934093414197</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.425950044691137</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.055996794569785</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-15.61429781779251</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="n">
+        <v>-0.7770398263017875</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,9; 0,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,43; 3,11</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-6,04; 0,7</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-18,59; 7,56</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1.463075958803407</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.504468614056839</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>-2.150463685286209</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +791,267 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,48</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,73</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>60,39%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-0,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-53,71%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.3612138922936732</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9161907781458478</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-2.219067718145642</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-2.898708757910612</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2.115211977241476</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.6132300315724832</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.3607439504928783</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,16; 2,43</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-1,87; 1,2</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,25; 0,82</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,96</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.900813980740502</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.4315488644200289</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.039637262135201</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-18.58643634977456</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.112084562571693</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.7018630496174388</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.561142768645515</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.4647220156100116</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.006358154534913136</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.4758659759762542</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.727317231482426</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.6039325256301575</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.008154883806606695</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.5371393791515302</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.157385588393094</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.865588418248649</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.24606295224501</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.430444306549626</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.204328651326075</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.8230117030566487</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>8.964498500328226</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,66</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-24,12%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-18,5%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-36,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,66; 0,85</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-1,15; 0,55</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,32; 0,87</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-7,05; 2,41</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-76,8; 389,36</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-73,59; 98,6</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-65,93; 126,33</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-90,42; 127,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.05519143296536495</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.2687236737178609</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.2630966996693263</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.657317290887217</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.09771030796655124</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.2411762847566024</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.1849929003580277</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.3659091201664524</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.6613498180508183</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.148829314535509</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.317886393158057</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-7.051049880257816</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.7680477337247315</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.7359289459559678</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.6593208707567378</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.9041606243637619</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.8533842969357939</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.5471221944555321</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.8732050977106874</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.413484040426134</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>3.893583245054383</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.9860010258533942</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>1.263341045380128</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>1.272075345212049</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1059,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
